--- a/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_tarapaca.xlsx
+++ b/output/graficos_envejecimiento/plot_comunal_d_enveje_a_2024_tarapaca.xlsx
@@ -432,7 +432,7 @@
         <v>21.34111394779347</v>
       </c>
       <c r="D4">
-        <v>63.18970457979471</v>
+        <v>63.18970457979472</v>
       </c>
       <c r="E4">
         <v>15.46918147241182</v>
@@ -445,13 +445,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>87.71929824561404</v>
+        <v>87.71929824561403</v>
       </c>
       <c r="C5">
-        <v>25.61797752808989</v>
+        <v>25.61797752808988</v>
       </c>
       <c r="D5">
-        <v>51.91011235955056</v>
+        <v>51.91011235955057</v>
       </c>
       <c r="E5">
         <v>22.47191011235955</v>
@@ -489,7 +489,7 @@
         <v>26.72811059907834</v>
       </c>
       <c r="D7">
-        <v>54.08163265306123</v>
+        <v>54.08163265306122</v>
       </c>
       <c r="E7">
         <v>19.19025674786043</v>
@@ -511,7 +511,7 @@
         <v>57.2435174746336</v>
       </c>
       <c r="E8">
-        <v>20.37767756482526</v>
+        <v>20.37767756482525</v>
       </c>
     </row>
   </sheetData>
